--- a/6-过程管理/运行记录类文件/工单记录文件/060303-变更审批表（安徽2）.xlsx
+++ b/6-过程管理/运行记录类文件/工单记录文件/060303-变更审批表（安徽2）.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="22188" windowHeight="9575" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="变更审批表" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -120,19 +121,26 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;\-;\-;@"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -140,6 +148,7 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -147,11 +156,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -159,23 +170,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -183,36 +198,41 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,6 +240,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -228,7 +249,8 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -236,6 +258,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -244,6 +267,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -252,6 +276,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -259,7 +284,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -267,7 +293,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,7 +302,8 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -283,14 +311,16 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,65 +328,52 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499588000122074"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -405,19 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,19 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,19 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,19 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,19 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -525,19 +542,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.04993"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,21 +571,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -578,7 +586,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -587,16 +594,14 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -611,7 +616,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -626,7 +630,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -641,7 +644,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -650,7 +652,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -661,276 +662,402 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="55">
+  <cellStyleXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="53" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="55">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Comma" xfId="49"/>
-    <cellStyle name="Comma [0]" xfId="50"/>
-    <cellStyle name="Currency" xfId="51"/>
-    <cellStyle name="Currency [0]" xfId="52"/>
-    <cellStyle name="Normal" xfId="53"/>
-    <cellStyle name="Percent" xfId="54"/>
+  <cellStyles count="69">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Percent" xfId="20"/>
+    <cellStyle name="Currency" xfId="21"/>
+    <cellStyle name="Currency [0]" xfId="22"/>
+    <cellStyle name="Comma" xfId="23"/>
+    <cellStyle name="Comma [0]" xfId="24"/>
+    <cellStyle name="Percent" xfId="25"/>
+    <cellStyle name="Currency" xfId="26"/>
+    <cellStyle name="Currency [0]" xfId="27"/>
+    <cellStyle name="Comma" xfId="28"/>
+    <cellStyle name="Comma [0]" xfId="29"/>
+    <cellStyle name="千位分隔" xfId="30"/>
+    <cellStyle name="货币" xfId="31"/>
+    <cellStyle name="百分比" xfId="32"/>
+    <cellStyle name="千位分隔[0]" xfId="33"/>
+    <cellStyle name="货币[0]" xfId="34"/>
+    <cellStyle name="超链接" xfId="35"/>
+    <cellStyle name="已访问的超链接" xfId="36"/>
+    <cellStyle name="注释" xfId="37"/>
+    <cellStyle name="警告文本" xfId="38"/>
+    <cellStyle name="标题" xfId="39"/>
+    <cellStyle name="解释性文本" xfId="40"/>
+    <cellStyle name="标题 1" xfId="41"/>
+    <cellStyle name="标题 2" xfId="42"/>
+    <cellStyle name="标题 3" xfId="43"/>
+    <cellStyle name="标题 4" xfId="44"/>
+    <cellStyle name="输入" xfId="45"/>
+    <cellStyle name="输出" xfId="46"/>
+    <cellStyle name="计算" xfId="47"/>
+    <cellStyle name="检查单元格" xfId="48"/>
+    <cellStyle name="链接单元格" xfId="49"/>
+    <cellStyle name="汇总" xfId="50"/>
+    <cellStyle name="好" xfId="51"/>
+    <cellStyle name="差" xfId="52"/>
+    <cellStyle name="适中" xfId="53"/>
+    <cellStyle name="强调文字颜色 1" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="55"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="56"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="57"/>
+    <cellStyle name="强调文字颜色 2" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="59"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="60"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="61"/>
+    <cellStyle name="强调文字颜色 3" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="63"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="64"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="65"/>
+    <cellStyle name="强调文字颜色 4" xfId="66"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="68"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="69"/>
+    <cellStyle name="强调文字颜色 5" xfId="70"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="72"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="73"/>
+    <cellStyle name="强调文字颜色 6" xfId="74"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="75"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="76"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="77"/>
+    <cellStyle name="Comma" xfId="78"/>
+    <cellStyle name="Comma [0]" xfId="79"/>
+    <cellStyle name="Currency" xfId="80"/>
+    <cellStyle name="Currency [0]" xfId="81"/>
+    <cellStyle name="Percent" xfId="82"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1225,17 +1352,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="16.6296296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6296296296296" customWidth="1"/>
-    <col min="3" max="3" width="14.8796296296296" customWidth="1"/>
+    <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
     <col min="4" max="4" width="32.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1" spans="1:4">
+    <row r="1" spans="1:4" ht="27" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1243,7 +1369,7 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" ht="20.25" customHeight="1" spans="1:4">
+    <row r="2" spans="1:4" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1257,7 +1383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:4">
+    <row r="3" spans="1:4" ht="21.75" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
@@ -1265,7 +1391,7 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="14.4">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -1279,7 +1405,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="24.95" customHeight="1" spans="1:4">
+    <row r="5" spans="1:4" ht="24.95" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -1293,7 +1419,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="13.7" customHeight="1" spans="1:4">
+    <row r="6" spans="1:4" ht="13.7" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
@@ -1307,19 +1433,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="13.7" customHeight="1" spans="1:4">
+    <row r="7" spans="1:4" ht="13.7" customHeight="1">
       <c r="A7" s="12"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13"/>
       <c r="D7" s="11"/>
     </row>
-    <row r="8" ht="13.7" customHeight="1" spans="1:4">
+    <row r="8" spans="1:4" ht="13.7" customHeight="1">
       <c r="A8" s="12"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
     </row>
-    <row r="9" ht="21" customHeight="1" spans="1:4">
+    <row r="9" spans="1:4" ht="21" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
@@ -1327,7 +1453,7 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="14.4">
       <c r="A10" s="9" t="s">
         <v>5</v>
       </c>
@@ -1341,7 +1467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="24.95" customHeight="1" spans="1:4">
+    <row r="11" spans="1:4" ht="24.95" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
@@ -1355,7 +1481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" ht="13.7" customHeight="1" spans="1:4">
+    <row r="12" spans="1:4" ht="13.7" customHeight="1">
       <c r="A12" s="14" t="s">
         <v>15</v>
       </c>
@@ -1369,19 +1495,19 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" ht="13.7" customHeight="1" spans="1:4">
+    <row r="13" spans="1:4" ht="13.7" customHeight="1">
       <c r="A13" s="12"/>
       <c r="B13" s="11"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
     </row>
-    <row r="14" ht="13.7" customHeight="1" spans="1:4">
+    <row r="14" spans="1:4" ht="13.7" customHeight="1">
       <c r="A14" s="12"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="14.4">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1389,7 +1515,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" ht="15.95" customHeight="1" spans="1:4">
+    <row r="16" spans="1:4" ht="15.95" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>18</v>
       </c>
@@ -1399,7 +1525,7 @@
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
     </row>
-    <row r="17" ht="14.65" customHeight="1" spans="1:4">
+    <row r="17" spans="1:4" ht="14.65" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="16" t="s">
         <v>20</v>
@@ -1407,7 +1533,7 @@
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
     </row>
-    <row r="18" ht="13.9" customHeight="1" spans="1:4">
+    <row r="18" spans="1:4" ht="13.9" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="16" t="s">
         <v>21</v>
@@ -1415,7 +1541,7 @@
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
     </row>
-    <row r="19" ht="20.85" customHeight="1" spans="1:4">
+    <row r="19" spans="1:4" ht="20.85" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>22</v>
       </c>
@@ -1425,7 +1551,7 @@
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
     </row>
-    <row r="20" ht="45.95" customHeight="1" spans="1:4">
+    <row r="20" spans="1:4" ht="45.95" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>24</v>
       </c>
@@ -1450,7 +1576,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.708661417322835" right="0.708661417322835" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>